--- a/local/agegroups/USAW-2026-08.xlsx
+++ b/local/agegroups/USAW-2026-08.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/nemikor/usaw-owlcms/local/agegroups/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F802939-D817-EA44-8A2E-82C365C2CF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BDE891-894E-634A-89CD-B183BF392DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="660" windowWidth="33020" windowHeight="21680" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1540" yWindow="660" windowWidth="33020" windowHeight="21680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AgeGroups" sheetId="1" r:id="rId1"/>
@@ -5397,10 +5397,16 @@
         <v>120</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N2">
         <v>2</v>
+      </c>
+      <c r="O2">
+        <v>5</v>
+      </c>
+      <c r="P2">
+        <v>5</v>
       </c>
       <c r="Q2" s="1"/>
       <c r="R2" t="b">
@@ -5442,10 +5448,16 @@
         <v>120</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N3">
         <v>2</v>
+      </c>
+      <c r="O3">
+        <v>5</v>
+      </c>
+      <c r="P3">
+        <v>5</v>
       </c>
       <c r="Q3" s="1"/>
       <c r="R3" t="b">
@@ -5487,10 +5499,16 @@
         <v>120</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N4">
         <v>2</v>
+      </c>
+      <c r="O4">
+        <v>5</v>
+      </c>
+      <c r="P4">
+        <v>5</v>
       </c>
       <c r="Q4" s="7"/>
       <c r="R4" t="b">
@@ -5532,10 +5550,16 @@
         <v>120</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N5">
         <v>2</v>
+      </c>
+      <c r="O5">
+        <v>5</v>
+      </c>
+      <c r="P5">
+        <v>5</v>
       </c>
       <c r="Q5" s="7"/>
       <c r="R5" t="b">
@@ -5577,10 +5601,16 @@
         <v>120</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N6">
         <v>2</v>
+      </c>
+      <c r="O6">
+        <v>5</v>
+      </c>
+      <c r="P6">
+        <v>5</v>
       </c>
       <c r="Q6" s="7"/>
       <c r="R6" t="b">
@@ -5622,10 +5652,16 @@
         <v>120</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N7">
         <v>2</v>
+      </c>
+      <c r="O7">
+        <v>5</v>
+      </c>
+      <c r="P7">
+        <v>5</v>
       </c>
       <c r="Q7" s="7"/>
       <c r="R7" t="b">
@@ -5664,10 +5700,16 @@
         <v>23</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N8">
         <v>2</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <v>5</v>
       </c>
       <c r="Q8" s="7"/>
       <c r="R8" t="b">
@@ -5706,10 +5748,16 @@
         <v>23</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N9">
         <v>2</v>
+      </c>
+      <c r="O9">
+        <v>5</v>
+      </c>
+      <c r="P9">
+        <v>5</v>
       </c>
       <c r="Q9" s="7"/>
       <c r="R9" t="b">

--- a/local/agegroups/USAW-2026-08.xlsx
+++ b/local/agegroups/USAW-2026-08.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/nemikor/usaw-owlcms/local/agegroups/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BDE891-894E-634A-89CD-B183BF392DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C52D2BA-2589-EC49-9A22-3115B5615699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="660" windowWidth="33020" windowHeight="21680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24400" yWindow="5920" windowWidth="33020" windowHeight="21680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AgeGroups" sheetId="1" r:id="rId1"/>
@@ -824,8 +824,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="5" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2">
         <v>30</v>
@@ -874,7 +873,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E3" s="4">
         <v>13</v>
@@ -1091,7 +1090,7 @@
         <v>7</v>
       </c>
       <c r="D7" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E7" s="4">
         <v>13</v>
@@ -3055,8 +3054,7 @@
         <v>11</v>
       </c>
       <c r="F46" s="5" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="2">
         <v>32</v>
@@ -3105,7 +3103,7 @@
         <v>29</v>
       </c>
       <c r="D47" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E47" s="4">
         <v>13</v>
@@ -3320,7 +3318,7 @@
         <v>29</v>
       </c>
       <c r="D51" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E51" s="4">
         <v>13</v>
